--- a/Documents/Product Catalog/Home/Oven Shelf.xlsx
+++ b/Documents/Product Catalog/Home/Oven Shelf.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Talukder Furniture\Documents\Product Catalog\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="d:\By Raj\Talukder Furniture\Documents\Product Catalog\Home\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4282391-F47A-4DF6-8F66-35FDD522D334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{666B0DBC-472C-442F-B1C0-7787205F5A04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -494,9 +494,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -517,6 +514,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1128,55 +1128,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="39.950000000000003" customHeight="1">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="29"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="28"/>
     </row>
     <row r="2" spans="1:46" ht="39.950000000000003" customHeight="1">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="30"/>
-      <c r="N2" s="30"/>
-      <c r="O2" s="30"/>
-      <c r="P2" s="30"/>
-      <c r="Q2" s="30"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="29"/>
+      <c r="N2" s="29"/>
+      <c r="O2" s="29"/>
+      <c r="P2" s="29"/>
+      <c r="Q2" s="29"/>
     </row>
     <row r="3" spans="1:46" ht="50.1" customHeight="1">
-      <c r="A3" s="31" t="s">
+      <c r="A3" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="25" t="s">
+      <c r="C3" s="32" t="s">
         <v>4</v>
       </c>
       <c r="D3" s="33" t="s">
@@ -1185,32 +1185,32 @@
       <c r="E3" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="F3" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="27"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="25" t="s">
+      <c r="G3" s="26"/>
+      <c r="H3" s="27"/>
+      <c r="I3" s="32" t="s">
         <v>8</v>
       </c>
       <c r="J3" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="K3" s="25" t="s">
+      <c r="K3" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="L3" s="25"/>
-      <c r="M3" s="26"/>
-      <c r="N3" s="25" t="s">
+      <c r="L3" s="32"/>
+      <c r="M3" s="25"/>
+      <c r="N3" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="25" t="s">
+      <c r="O3" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="P3" s="25" t="s">
+      <c r="P3" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="Q3" s="25" t="s">
+      <c r="Q3" s="32" t="s">
         <v>24</v>
       </c>
       <c r="S3" s="4"/>
@@ -1243,9 +1243,9 @@
       <c r="AT3" s="4"/>
     </row>
     <row r="4" spans="1:46" ht="33.200000000000003" customHeight="1">
-      <c r="A4" s="32"/>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
+      <c r="A4" s="31"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
       <c r="D4" s="34"/>
       <c r="E4" s="34"/>
       <c r="F4" s="24" t="s">
@@ -1257,7 +1257,7 @@
       <c r="H4" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="25"/>
+      <c r="I4" s="32"/>
       <c r="J4" s="34"/>
       <c r="K4" s="5" t="s">
         <v>15</v>
@@ -1268,10 +1268,10 @@
       <c r="M4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="N4" s="25"/>
-      <c r="O4" s="25"/>
-      <c r="P4" s="25"/>
-      <c r="Q4" s="25"/>
+      <c r="N4" s="32"/>
+      <c r="O4" s="32"/>
+      <c r="P4" s="32"/>
+      <c r="Q4" s="32"/>
       <c r="S4" s="4"/>
       <c r="T4" s="4"/>
       <c r="U4" s="4"/>
